--- a/documentation/Jake_Markees_Felix_SprintBacklogBurndown.xlsx
+++ b/documentation/Jake_Markees_Felix_SprintBacklogBurndown.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakemiranda/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B6B796A-C763-4E74-9494-7FC01D90B009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73D5C993-13C1-48C1-84EA-6641AF3B9134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>Who's Task</t>
   </si>
@@ -53,7 +50,7 @@
     <t>Initial Estimate</t>
   </si>
   <si>
-    <t>Amount Remaining After…</t>
+    <t>Hours Remaining</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -68,6 +65,15 @@
     <t>Week 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Jake </t>
+  </si>
+  <si>
+    <t>CrewMate Login</t>
+  </si>
+  <si>
+    <t>Fix failing test in logging in. TryLoginFailsWithInvalidCredentials</t>
+  </si>
+  <si>
     <t>Jake</t>
   </si>
   <si>
@@ -78,9 +84,6 @@
   </si>
   <si>
     <t>Fix and add Unit test to all classes in storage package to achieve 100% branch coverage with new Stock type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake </t>
   </si>
   <si>
     <t>Fix and add Unit test to all viewmodel class that interact with stock to achieve 100% branch coverage with new Stock type</t>
@@ -259,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -268,6 +271,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -383,15 +387,15 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Sheet1!$D$31:$H$31</c:f>
+              <c:f>Sheet1!D32:H32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>21.75</c:v>
+                  <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1144,13 +1148,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1179,37 +1183,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="31">
-          <cell r="D31">
-            <v>21.75</v>
-          </cell>
-          <cell r="E31">
-            <v>0</v>
-          </cell>
-          <cell r="F31">
-            <v>0</v>
-          </cell>
-          <cell r="G31">
-            <v>0</v>
-          </cell>
-          <cell r="H31">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1475,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A44282-E778-465E-AF6B-3E67CA5791EA}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -1485,30 +1458,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
       <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1533,45 +1506,51 @@
         <v>11</v>
       </c>
       <c r="D3" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1581,364 +1560,404 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1">
         <v>0.5</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D16" s="1">
         <v>0.5</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1">
         <v>0.75</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E21" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E23" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" s="1">
         <v>0.5</v>
       </c>
-      <c r="E24" s="2"/>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D25" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E25" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>40</v>
@@ -1949,104 +1968,134 @@
       <c r="D26" s="1">
         <v>1.5</v>
       </c>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2">
+        <v>1.5</v>
+      </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.5</v>
+      </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="C31" s="4" t="s">
+      <c r="A31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="3">
-        <f>SUM(D3:D30)</f>
-        <v>23.25</v>
-      </c>
-      <c r="E31" s="3">
-        <f t="shared" ref="E31:H31" si="0">SUM(E3:E26)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
+      <c r="C31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="C32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="3">
+        <f>SUM(D3:D31)</f>
+        <v>23.5</v>
+      </c>
+      <c r="E32" s="3">
+        <f>SUM(E3:E31)</f>
+        <v>9</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" ref="E32:H32" si="0">SUM(F4:F27)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G31" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
+      <c r="H32" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
